--- a/data/trans_orig/P36B14-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B14-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de refrescos con azúcar en 2016</t>
+          <t>Población según la frecuencia de consumo de refrescos con azúcar en 2016 (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96950</t>
+          <t>96994</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133105</t>
+          <t>131861</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122946</t>
+          <t>123938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157648</t>
+          <t>158152</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>230540</t>
+          <t>229858</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>279744</t>
+          <t>279429</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21540</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42730</t>
+          <t>43304</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15939</t>
+          <t>15588</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35948</t>
+          <t>33597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41983</t>
+          <t>42133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72102</t>
+          <t>69688</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35616</t>
+          <t>35314</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61065</t>
+          <t>61882</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40015</t>
+          <t>40565</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67922</t>
+          <t>68368</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>79421</t>
+          <t>81274</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118523</t>
+          <t>120379</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40745</t>
+          <t>40995</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69478</t>
+          <t>68934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23375</t>
+          <t>22744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44601</t>
+          <t>43148</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69877</t>
+          <t>71077</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105580</t>
+          <t>104817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34607</t>
+          <t>34257</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61348</t>
+          <t>61932</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29434</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53090</t>
+          <t>52890</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71357</t>
+          <t>69657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106272</t>
+          <t>106527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104914</t>
+          <t>106173</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142471</t>
+          <t>146215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136463</t>
+          <t>136412</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180450</t>
+          <t>180457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>253195</t>
+          <t>249559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>314808</t>
+          <t>311264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60242</t>
+          <t>59800</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92837</t>
+          <t>91925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68829</t>
+          <t>68799</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103036</t>
+          <t>105830</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139084</t>
+          <t>137115</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188328</t>
+          <t>187656</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80176</t>
+          <t>79289</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>113739</t>
+          <t>114933</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78174</t>
+          <t>76755</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113713</t>
+          <t>113088</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>167143</t>
+          <t>168266</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>219630</t>
+          <t>219449</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106092</t>
+          <t>105737</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146021</t>
+          <t>143799</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102520</t>
+          <t>102966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141477</t>
+          <t>142430</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>220884</t>
+          <t>222135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273439</t>
+          <t>276768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65153</t>
+          <t>64560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98518</t>
+          <t>98213</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47253</t>
+          <t>48227</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77393</t>
+          <t>78480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122254</t>
+          <t>121332</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166170</t>
+          <t>166558</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55628</t>
+          <t>56610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83874</t>
+          <t>84894</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92235</t>
+          <t>91774</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126521</t>
+          <t>125349</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>156033</t>
+          <t>155597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>202457</t>
+          <t>201242</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66426</t>
+          <t>64815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98578</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67209</t>
+          <t>67431</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97924</t>
+          <t>98543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140986</t>
+          <t>141534</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>185871</t>
+          <t>184376</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79090</t>
+          <t>79757</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>110563</t>
+          <t>111633</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69981</t>
+          <t>70160</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>101443</t>
+          <t>100522</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>156383</t>
+          <t>156252</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>199741</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43991</t>
+          <t>44279</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70964</t>
+          <t>70739</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41754</t>
+          <t>43912</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68416</t>
+          <t>69438</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93411</t>
+          <t>94537</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131595</t>
+          <t>131287</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21944</t>
+          <t>21487</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12324</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29685</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>135680</t>
+          <t>135863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>173283</t>
+          <t>175781</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162855</t>
+          <t>164349</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203139</t>
+          <t>203854</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>311059</t>
+          <t>307463</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>366642</t>
+          <t>365237</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51088</t>
+          <t>50360</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80338</t>
+          <t>80661</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>61359</t>
+          <t>59668</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>93514</t>
+          <t>92089</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>119871</t>
+          <t>118824</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>163560</t>
+          <t>161575</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28037</t>
+          <t>28519</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52570</t>
+          <t>51424</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31273</t>
+          <t>31209</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56188</t>
+          <t>57827</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>65927</t>
+          <t>63942</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>98471</t>
+          <t>99166</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22587</t>
+          <t>22915</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46108</t>
+          <t>45684</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13773</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32491</t>
+          <t>32111</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41684</t>
+          <t>39316</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71216</t>
+          <t>70719</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>63167</t>
+          <t>63192</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>94474</t>
+          <t>95744</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47436</t>
+          <t>48164</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75632</t>
+          <t>76749</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>120515</t>
+          <t>118449</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>163261</t>
+          <t>162502</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48213</t>
+          <t>48664</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>72892</t>
+          <t>73055</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>63697</t>
+          <t>63509</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>91961</t>
+          <t>90720</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>117153</t>
+          <t>118182</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>155317</t>
+          <t>156402</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28190</t>
+          <t>27737</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>50259</t>
+          <t>49982</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>41726</t>
+          <t>42848</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>65961</t>
+          <t>67103</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>75178</t>
+          <t>75342</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>108560</t>
+          <t>109090</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22142</t>
+          <t>21783</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42305</t>
+          <t>41982</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18717</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37071</t>
+          <t>37133</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>45954</t>
+          <t>45707</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>73175</t>
+          <t>74202</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>31664</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>54924</t>
+          <t>54578</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>22079</t>
+          <t>21492</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>42529</t>
+          <t>41373</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>58452</t>
+          <t>58507</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>88728</t>
+          <t>88575</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29054</t>
+          <t>29499</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>52325</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>21173</t>
+          <t>21793</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40926</t>
+          <t>42435</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>55704</t>
+          <t>55946</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>87182</t>
+          <t>86947</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>106399</t>
+          <t>108450</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>141576</t>
+          <t>140631</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>116539</t>
+          <t>117240</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>150151</t>
+          <t>148740</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>234450</t>
+          <t>232502</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>283411</t>
+          <t>279444</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>29669</t>
+          <t>29544</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>53802</t>
+          <t>52783</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>33654</t>
+          <t>33857</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>58602</t>
+          <t>58284</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>68948</t>
+          <t>69770</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>105209</t>
+          <t>102826</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>41336</t>
+          <t>42001</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>56576</t>
+          <t>57086</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>58562</t>
+          <t>58660</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>90628</t>
+          <t>93033</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>24099</t>
+          <t>24121</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>46454</t>
+          <t>43681</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>37141</t>
+          <t>37634</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>46028</t>
+          <t>46365</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>75417</t>
+          <t>74854</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>47445</t>
+          <t>45906</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>35112</t>
+          <t>33292</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>46032</t>
+          <t>46479</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>73615</t>
+          <t>74956</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>200640</t>
+          <t>198781</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>251453</t>
+          <t>250651</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>243959</t>
+          <t>240845</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>294503</t>
+          <t>291685</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>459809</t>
+          <t>455308</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>529244</t>
+          <t>529878</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>92789</t>
+          <t>93653</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>135812</t>
+          <t>134084</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>106623</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>150276</t>
+          <t>150797</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>213655</t>
+          <t>210411</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>270306</t>
+          <t>271193</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>103692</t>
+          <t>103185</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>145206</t>
+          <t>145346</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>69339</t>
+          <t>69859</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>105507</t>
+          <t>104820</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>184039</t>
+          <t>181152</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>236426</t>
+          <t>236910</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>71626</t>
+          <t>72840</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>112056</t>
+          <t>108986</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>56267</t>
+          <t>57849</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>87885</t>
+          <t>89293</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>136360</t>
+          <t>138115</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>185490</t>
+          <t>187688</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>76812</t>
+          <t>75866</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>113026</t>
+          <t>113495</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>103094</t>
+          <t>103549</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>143907</t>
+          <t>144030</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>190071</t>
+          <t>191302</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>243744</t>
+          <t>246308</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>172540</t>
+          <t>173399</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>222146</t>
+          <t>221990</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>205353</t>
+          <t>205250</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>259007</t>
+          <t>259701</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>390982</t>
+          <t>392342</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>466752</t>
+          <t>465547</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>73285</t>
+          <t>72024</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>109888</t>
+          <t>110437</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>75960</t>
+          <t>76054</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>115064</t>
+          <t>115110</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>161274</t>
+          <t>159833</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>212894</t>
+          <t>213115</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>134096</t>
+          <t>133673</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>177496</t>
+          <t>178897</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>146588</t>
+          <t>149030</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>195082</t>
+          <t>196601</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>298598</t>
+          <t>295894</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>364097</t>
+          <t>361293</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>170491</t>
+          <t>169139</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>217585</t>
+          <t>217343</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>180075</t>
+          <t>179647</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>229890</t>
+          <t>229959</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>365603</t>
+          <t>357984</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>433022</t>
+          <t>428853</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>118979</t>
+          <t>118092</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>160351</t>
+          <t>163230</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>103299</t>
+          <t>102455</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>141760</t>
+          <t>141880</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>230734</t>
+          <t>232129</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>292781</t>
+          <t>292352</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1009521</t>
+          <t>1016057</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1121586</t>
+          <t>1124840</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1236228</t>
+          <t>1241152</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1357265</t>
+          <t>1357914</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2289214</t>
+          <t>2291401</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2439943</t>
+          <t>2452599</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>488272</t>
+          <t>493512</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>579916</t>
+          <t>579744</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>541441</t>
+          <t>541756</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>631440</t>
+          <t>632915</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1055100</t>
+          <t>1060499</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1185675</t>
+          <t>1183688</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>569173</t>
+          <t>572154</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>661902</t>
+          <t>665401</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>559677</t>
+          <t>563244</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>651913</t>
+          <t>652079</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1163119</t>
+          <t>1161984</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1285691</t>
+          <t>1295175</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>586150</t>
+          <t>582041</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>674847</t>
+          <t>677375</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>520070</t>
+          <t>514636</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>609413</t>
+          <t>608232</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1127649</t>
+          <t>1130901</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1254806</t>
+          <t>1254060</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>483864</t>
+          <t>481946</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>572674</t>
+          <t>570117</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>430332</t>
+          <t>429255</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>509047</t>
+          <t>507796</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>935650</t>
+          <t>933163</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1053818</t>
+          <t>1049478</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B14-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B14-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96994</t>
+          <t>96246</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131861</t>
+          <t>131916</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123938</t>
+          <t>123199</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158152</t>
+          <t>157769</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>229858</t>
+          <t>231361</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>279429</t>
+          <t>278704</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,85%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21283</t>
+          <t>21254</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43304</t>
+          <t>42030</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33597</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42133</t>
+          <t>43063</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69688</t>
+          <t>73298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35314</t>
+          <t>34981</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61882</t>
+          <t>61159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40565</t>
+          <t>39974</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68368</t>
+          <t>67050</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81274</t>
+          <t>80310</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>120379</t>
+          <t>120375</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40995</t>
+          <t>43146</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68934</t>
+          <t>69386</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22744</t>
+          <t>22409</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43148</t>
+          <t>43016</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71077</t>
+          <t>70710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104817</t>
+          <t>105202</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34257</t>
+          <t>35776</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61932</t>
+          <t>62657</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28738</t>
+          <t>29050</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52890</t>
+          <t>52077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69657</t>
+          <t>70241</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106527</t>
+          <t>105425</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106173</t>
+          <t>103834</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146215</t>
+          <t>142935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136412</t>
+          <t>138724</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180457</t>
+          <t>180856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>249559</t>
+          <t>253230</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>311264</t>
+          <t>314581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59800</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91925</t>
+          <t>92797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68799</t>
+          <t>69413</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105830</t>
+          <t>102403</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>137115</t>
+          <t>140028</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187656</t>
+          <t>186354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79289</t>
+          <t>79272</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>114933</t>
+          <t>116289</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76755</t>
+          <t>78312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113088</t>
+          <t>114072</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>168266</t>
+          <t>167667</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>219449</t>
+          <t>217568</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105737</t>
+          <t>106162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>143799</t>
+          <t>146291</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102966</t>
+          <t>100561</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142430</t>
+          <t>139256</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>222135</t>
+          <t>216844</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>276768</t>
+          <t>275880</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64560</t>
+          <t>65819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98213</t>
+          <t>100494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48227</t>
+          <t>47503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78480</t>
+          <t>76476</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>121332</t>
+          <t>121645</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166558</t>
+          <t>167212</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56610</t>
+          <t>55991</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84894</t>
+          <t>84802</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91774</t>
+          <t>93376</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125349</t>
+          <t>126854</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>155597</t>
+          <t>155593</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201242</t>
+          <t>203157</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64815</t>
+          <t>65886</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95512</t>
+          <t>95528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67431</t>
+          <t>66283</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98543</t>
+          <t>98337</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141534</t>
+          <t>140680</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>184376</t>
+          <t>188293</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79757</t>
+          <t>79897</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111633</t>
+          <t>110840</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70160</t>
+          <t>69579</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100522</t>
+          <t>99979</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>156252</t>
+          <t>155829</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>199741</t>
+          <t>200643</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44279</t>
+          <t>44466</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70739</t>
+          <t>69764</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43912</t>
+          <t>42663</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69438</t>
+          <t>69561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94537</t>
+          <t>95242</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131287</t>
+          <t>131531</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29056</t>
+          <t>28810</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>135863</t>
+          <t>136197</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>175781</t>
+          <t>174318</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164349</t>
+          <t>161889</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203854</t>
+          <t>203211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>307463</t>
+          <t>311188</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>365237</t>
+          <t>368468</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,87%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50360</t>
+          <t>51715</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80661</t>
+          <t>80465</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59668</t>
+          <t>59996</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>92089</t>
+          <t>92058</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>118824</t>
+          <t>119596</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>161575</t>
+          <t>164079</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28519</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51424</t>
+          <t>52473</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31209</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57827</t>
+          <t>55442</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>63942</t>
+          <t>65287</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>99166</t>
+          <t>98860</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22915</t>
+          <t>23447</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>45186</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>13882</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32111</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39316</t>
+          <t>41913</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70719</t>
+          <t>69782</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>63192</t>
+          <t>63524</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>95744</t>
+          <t>96695</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48164</t>
+          <t>48063</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>76749</t>
+          <t>75964</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>118449</t>
+          <t>118281</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>162502</t>
+          <t>160753</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>47872</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73055</t>
+          <t>73541</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>63509</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>90720</t>
+          <t>91523</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>118182</t>
+          <t>118456</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>156402</t>
+          <t>156904</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>27345</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49982</t>
+          <t>49956</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>42848</t>
+          <t>41693</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>67103</t>
+          <t>66161</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>75342</t>
+          <t>75132</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>109090</t>
+          <t>111456</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21783</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41982</t>
+          <t>42481</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18830</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37133</t>
+          <t>38301</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>45707</t>
+          <t>46268</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>74202</t>
+          <t>72705</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31664</t>
+          <t>33086</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>54578</t>
+          <t>55338</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21492</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>41373</t>
+          <t>42167</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>58507</t>
+          <t>58394</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>88575</t>
+          <t>88925</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>28889</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>52325</t>
+          <t>51199</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>21793</t>
+          <t>21120</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>40360</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>55946</t>
+          <t>56418</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>86947</t>
+          <t>87253</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>108450</t>
+          <t>108025</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>140631</t>
+          <t>141777</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>117240</t>
+          <t>118296</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>148740</t>
+          <t>151013</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>232502</t>
+          <t>234658</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>279444</t>
+          <t>281415</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,48%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>29544</t>
+          <t>30823</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>52783</t>
+          <t>54082</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>33857</t>
+          <t>33979</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>58284</t>
+          <t>58370</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>69770</t>
+          <t>69924</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>102826</t>
+          <t>104474</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>20508</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>42001</t>
+          <t>41177</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>33124</t>
+          <t>33145</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>57086</t>
+          <t>57161</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>58660</t>
+          <t>57827</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>93033</t>
+          <t>92015</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>24121</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>43681</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>17670</t>
+          <t>17558</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>37634</t>
+          <t>36040</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>46365</t>
+          <t>46412</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>74854</t>
+          <t>76770</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>24273</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>45906</t>
+          <t>47427</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>33292</t>
+          <t>35104</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>46479</t>
+          <t>45117</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>74956</t>
+          <t>74651</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>198781</t>
+          <t>200601</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>250651</t>
+          <t>252620</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>240845</t>
+          <t>244182</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>291685</t>
+          <t>295164</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>455308</t>
+          <t>453211</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>529878</t>
+          <t>530446</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>93653</t>
+          <t>93421</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>134084</t>
+          <t>134619</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>106623</t>
+          <t>108680</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>150797</t>
+          <t>150837</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>210411</t>
+          <t>212118</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>271193</t>
+          <t>270255</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>103185</t>
+          <t>104190</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>145346</t>
+          <t>145961</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>69859</t>
+          <t>71433</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>104820</t>
+          <t>106502</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>181152</t>
+          <t>181326</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>236910</t>
+          <t>236953</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>72840</t>
+          <t>72813</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>108986</t>
+          <t>110177</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>57849</t>
+          <t>55542</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>89293</t>
+          <t>89820</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>138115</t>
+          <t>135725</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>187688</t>
+          <t>185397</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>75866</t>
+          <t>76119</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>113495</t>
+          <t>114108</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>103549</t>
+          <t>102857</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>144030</t>
+          <t>142622</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>191302</t>
+          <t>189533</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>246308</t>
+          <t>244385</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>173399</t>
+          <t>170289</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>221990</t>
+          <t>219611</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>205250</t>
+          <t>205635</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>259701</t>
+          <t>256933</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>392342</t>
+          <t>393011</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>465547</t>
+          <t>463110</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>72024</t>
+          <t>73578</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>110437</t>
+          <t>109259</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>76054</t>
+          <t>77349</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>115110</t>
+          <t>115506</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>159833</t>
+          <t>159858</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>213115</t>
+          <t>211142</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>133673</t>
+          <t>135731</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>178897</t>
+          <t>179832</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>149030</t>
+          <t>151107</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>196601</t>
+          <t>197762</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>295894</t>
+          <t>299394</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>361293</t>
+          <t>362487</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>169139</t>
+          <t>169985</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>217343</t>
+          <t>219177</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>179647</t>
+          <t>178705</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>229959</t>
+          <t>229014</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>357984</t>
+          <t>363171</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>428853</t>
+          <t>435937</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>118092</t>
+          <t>118491</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>163230</t>
+          <t>162052</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>102455</t>
+          <t>104226</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>141880</t>
+          <t>145234</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>232129</t>
+          <t>230619</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>292352</t>
+          <t>292082</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1016057</t>
+          <t>1013835</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1124840</t>
+          <t>1124029</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1241152</t>
+          <t>1239405</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1357914</t>
+          <t>1356050</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2291401</t>
+          <t>2288910</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2452599</t>
+          <t>2445072</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>493512</t>
+          <t>487730</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>579744</t>
+          <t>580383</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>541756</t>
+          <t>545281</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>632915</t>
+          <t>631415</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1060499</t>
+          <t>1052328</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1183688</t>
+          <t>1181943</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>572154</t>
+          <t>571734</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>665401</t>
+          <t>662270</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>563244</t>
+          <t>558737</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>652079</t>
+          <t>652614</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1161984</t>
+          <t>1160180</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1295175</t>
+          <t>1285395</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>582041</t>
+          <t>582847</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>677375</t>
+          <t>676407</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>514636</t>
+          <t>522344</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>608232</t>
+          <t>610335</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1130901</t>
+          <t>1125167</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1254060</t>
+          <t>1253831</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>481946</t>
+          <t>484555</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>570117</t>
+          <t>567761</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>429255</t>
+          <t>429029</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>507796</t>
+          <t>507925</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>933163</t>
+          <t>931751</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1049478</t>
+          <t>1054926</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
